--- a/data/nzd0058/nzd0058.xlsx
+++ b/data/nzd0058/nzd0058.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H320"/>
+  <dimension ref="A1:H322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10022,6 +10022,66 @@
         <v>365.58</v>
       </c>
       <c r="H320" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>297.48</v>
+      </c>
+      <c r="C321" t="n">
+        <v>334.86</v>
+      </c>
+      <c r="D321" t="n">
+        <v>369.04</v>
+      </c>
+      <c r="E321" t="n">
+        <v>379.08</v>
+      </c>
+      <c r="F321" t="n">
+        <v>357.86</v>
+      </c>
+      <c r="G321" t="n">
+        <v>364.47</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>298.05</v>
+      </c>
+      <c r="C322" t="n">
+        <v>333.85</v>
+      </c>
+      <c r="D322" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="E322" t="n">
+        <v>379.5</v>
+      </c>
+      <c r="F322" t="n">
+        <v>358.85</v>
+      </c>
+      <c r="G322" t="n">
+        <v>365.32</v>
+      </c>
+      <c r="H322" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10038,7 +10098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B361"/>
+  <dimension ref="A1:B363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13651,6 +13711,26 @@
       </c>
       <c r="B361" t="n">
         <v>0.86</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -13819,28 +13899,28 @@
         <v>0.0276</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4151083938237832</v>
+        <v>0.3864312068018902</v>
       </c>
       <c r="J2" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0540602663570936</v>
+        <v>0.04682753863606881</v>
       </c>
       <c r="M2" t="n">
-        <v>9.940587419965507</v>
+        <v>9.990332116200479</v>
       </c>
       <c r="N2" t="n">
-        <v>164.3001082794999</v>
+        <v>166.7393598226609</v>
       </c>
       <c r="O2" t="n">
-        <v>12.81796037907357</v>
+        <v>12.91275957426068</v>
       </c>
       <c r="P2" t="n">
-        <v>310.345152180246</v>
+        <v>310.6664774066144</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -13901,28 +13981,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5604894577477304</v>
+        <v>0.5555221349862619</v>
       </c>
       <c r="J3" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K3" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2201518376633426</v>
+        <v>0.2190172334454776</v>
       </c>
       <c r="M3" t="n">
-        <v>5.767210358955697</v>
+        <v>5.756572376520483</v>
       </c>
       <c r="N3" t="n">
-        <v>60.63901903058949</v>
+        <v>60.36559561898814</v>
       </c>
       <c r="O3" t="n">
-        <v>7.787105947050515</v>
+        <v>7.769529948393799</v>
       </c>
       <c r="P3" t="n">
-        <v>323.3538348573477</v>
+        <v>323.4094968542481</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13979,28 +14059,28 @@
         <v>0.1037</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5403315037749657</v>
+        <v>0.5438557637564524</v>
       </c>
       <c r="J4" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K4" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2949657092869946</v>
+        <v>0.3000947994203185</v>
       </c>
       <c r="M4" t="n">
-        <v>4.416829043421478</v>
+        <v>4.403881536183919</v>
       </c>
       <c r="N4" t="n">
-        <v>38.0267159706372</v>
+        <v>37.84180243636234</v>
       </c>
       <c r="O4" t="n">
-        <v>6.166580573594834</v>
+        <v>6.151569103599694</v>
       </c>
       <c r="P4" t="n">
-        <v>351.2933563115444</v>
+        <v>351.2538687246862</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14057,28 +14137,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4594300376316398</v>
+        <v>0.4659377723462</v>
       </c>
       <c r="J5" t="n">
+        <v>321</v>
+      </c>
+      <c r="K5" t="n">
         <v>319</v>
       </c>
-      <c r="K5" t="n">
-        <v>317</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2282667043632053</v>
+        <v>0.2347491993819311</v>
       </c>
       <c r="M5" t="n">
-        <v>4.939600428172584</v>
+        <v>4.942180404718401</v>
       </c>
       <c r="N5" t="n">
-        <v>38.82820751147641</v>
+        <v>38.76333118054458</v>
       </c>
       <c r="O5" t="n">
-        <v>6.231228411114169</v>
+        <v>6.226020493103487</v>
       </c>
       <c r="P5" t="n">
-        <v>361.5121135409891</v>
+        <v>361.4390485059359</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14135,28 +14215,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1700167311362028</v>
+        <v>0.170243108836956</v>
       </c>
       <c r="J6" t="n">
+        <v>321</v>
+      </c>
+      <c r="K6" t="n">
         <v>319</v>
       </c>
-      <c r="K6" t="n">
-        <v>317</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.08807048996619449</v>
+        <v>0.08932144022195576</v>
       </c>
       <c r="M6" t="n">
-        <v>3.223191054477369</v>
+        <v>3.205999084919203</v>
       </c>
       <c r="N6" t="n">
-        <v>16.28538693322147</v>
+        <v>16.18505049495112</v>
       </c>
       <c r="O6" t="n">
-        <v>4.035515696069273</v>
+        <v>4.023064813665214</v>
       </c>
       <c r="P6" t="n">
-        <v>353.582105783886</v>
+        <v>353.5795609581617</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14213,28 +14293,28 @@
         <v>0.1507</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2204227091653198</v>
+        <v>0.2197822189379469</v>
       </c>
       <c r="J7" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K7" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07934816135723144</v>
+        <v>0.07986301534354801</v>
       </c>
       <c r="M7" t="n">
-        <v>4.611431696932209</v>
+        <v>4.585696506387761</v>
       </c>
       <c r="N7" t="n">
-        <v>30.59132466595116</v>
+        <v>30.40298053762023</v>
       </c>
       <c r="O7" t="n">
-        <v>5.530942475378962</v>
+        <v>5.513889782868373</v>
       </c>
       <c r="P7" t="n">
-        <v>359.4773883375485</v>
+        <v>359.48458219542</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14272,7 +14352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H320"/>
+  <dimension ref="A1:H322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27683,6 +27763,90 @@
         </is>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>-35.12295789835985,173.97976842188987</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>-35.12291536866759,173.98076486520495</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>-35.12282721869054,173.98172664177866</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-35.12276895732819,173.98261718615115</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-35.122965635806416,173.98351210638432</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-35.12290604969861,173.98441016341766</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-35.12295310291461,173.97977067158104</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>-35.12292399902755,173.98076132802152</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>-35.12283166997633,173.98172577276208</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-35.12276517117157,173.98261727589005</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-35.12295670963872,173.98351207619243</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-35.12289838594623,173.98441010366716</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0058/nzd0058.xlsx
+++ b/data/nzd0058/nzd0058.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H322"/>
+  <dimension ref="A1:H325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10084,6 +10084,96 @@
       <c r="H322" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>298.26</v>
+      </c>
+      <c r="C323" t="n">
+        <v>333.58</v>
+      </c>
+      <c r="D323" t="n">
+        <v>368.47</v>
+      </c>
+      <c r="E323" t="n">
+        <v>378.44</v>
+      </c>
+      <c r="F323" t="n">
+        <v>359.26</v>
+      </c>
+      <c r="G323" t="n">
+        <v>365.23</v>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="C324" t="n">
+        <v>332.27</v>
+      </c>
+      <c r="D324" t="n">
+        <v>368.8</v>
+      </c>
+      <c r="E324" t="n">
+        <v>379.24</v>
+      </c>
+      <c r="F324" t="n">
+        <v>360.31</v>
+      </c>
+      <c r="G324" t="n">
+        <v>366.25</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>296.55</v>
+      </c>
+      <c r="C325" t="n">
+        <v>331.64</v>
+      </c>
+      <c r="D325" t="n">
+        <v>368.48</v>
+      </c>
+      <c r="E325" t="n">
+        <v>379.21</v>
+      </c>
+      <c r="F325" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="G325" t="n">
+        <v>366.53</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B363"/>
+  <dimension ref="A1:B366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13731,6 +13821,36 @@
       </c>
       <c r="B363" t="n">
         <v>0.47</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -13899,28 +14019,28 @@
         <v>0.0276</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3864312068018902</v>
+        <v>0.3449630679017537</v>
       </c>
       <c r="J2" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K2" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04682753863606881</v>
+        <v>0.03729009184529375</v>
       </c>
       <c r="M2" t="n">
-        <v>9.990332116200479</v>
+        <v>10.0719025682376</v>
       </c>
       <c r="N2" t="n">
-        <v>166.7393598226609</v>
+        <v>170.1635145911077</v>
       </c>
       <c r="O2" t="n">
-        <v>12.91275957426068</v>
+        <v>13.04467380163673</v>
       </c>
       <c r="P2" t="n">
-        <v>310.6664774066144</v>
+        <v>311.1322434179144</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -13981,28 +14101,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5555221349862619</v>
+        <v>0.5450399849836298</v>
       </c>
       <c r="J3" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K3" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2190172334454776</v>
+        <v>0.2148553840124844</v>
       </c>
       <c r="M3" t="n">
-        <v>5.756572376520483</v>
+        <v>5.75673723121721</v>
       </c>
       <c r="N3" t="n">
-        <v>60.36559561898814</v>
+        <v>60.12836561084445</v>
       </c>
       <c r="O3" t="n">
-        <v>7.769529948393799</v>
+        <v>7.754248229895949</v>
       </c>
       <c r="P3" t="n">
-        <v>323.4094968542481</v>
+        <v>323.5272411205744</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14059,28 +14179,28 @@
         <v>0.1037</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5438557637564524</v>
+        <v>0.5485042563015373</v>
       </c>
       <c r="J4" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K4" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3000947994203185</v>
+        <v>0.3073576630919351</v>
       </c>
       <c r="M4" t="n">
-        <v>4.403881536183919</v>
+        <v>4.382620584170861</v>
       </c>
       <c r="N4" t="n">
-        <v>37.84180243636234</v>
+        <v>37.55296630251635</v>
       </c>
       <c r="O4" t="n">
-        <v>6.151569103599694</v>
+        <v>6.128047511444111</v>
       </c>
       <c r="P4" t="n">
-        <v>351.2538687246862</v>
+        <v>351.2016586140957</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14137,28 +14257,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4659377723462</v>
+        <v>0.4746720859800192</v>
       </c>
       <c r="J5" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K5" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2347491993819311</v>
+        <v>0.2439194242836189</v>
       </c>
       <c r="M5" t="n">
-        <v>4.942180404718401</v>
+        <v>4.94065767225305</v>
       </c>
       <c r="N5" t="n">
-        <v>38.76333118054458</v>
+        <v>38.62353234178853</v>
       </c>
       <c r="O5" t="n">
-        <v>6.226020493103487</v>
+        <v>6.214783370463409</v>
       </c>
       <c r="P5" t="n">
-        <v>361.4390485059359</v>
+        <v>361.3407479481102</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14215,28 +14335,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.170243108836956</v>
+        <v>0.1733183078845237</v>
       </c>
       <c r="J6" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K6" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08932144022195576</v>
+        <v>0.09372414421991881</v>
       </c>
       <c r="M6" t="n">
-        <v>3.205999084919203</v>
+        <v>3.190666283808984</v>
       </c>
       <c r="N6" t="n">
-        <v>16.18505049495112</v>
+        <v>16.06351993718102</v>
       </c>
       <c r="O6" t="n">
-        <v>4.023064813665214</v>
+        <v>4.007932127317155</v>
       </c>
       <c r="P6" t="n">
-        <v>353.5795609581617</v>
+        <v>353.5449468829076</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14293,28 +14413,28 @@
         <v>0.1507</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2197822189379469</v>
+        <v>0.2208107213077131</v>
       </c>
       <c r="J7" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K7" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07986301534354801</v>
+        <v>0.08195586201950611</v>
       </c>
       <c r="M7" t="n">
-        <v>4.585696506387761</v>
+        <v>4.549962645098764</v>
       </c>
       <c r="N7" t="n">
-        <v>30.40298053762023</v>
+        <v>30.12648741877541</v>
       </c>
       <c r="O7" t="n">
-        <v>5.513889782868373</v>
+        <v>5.488760098489951</v>
       </c>
       <c r="P7" t="n">
-        <v>359.48458219542</v>
+        <v>359.4729901296399</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14352,7 +14472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H322"/>
+  <dimension ref="A1:H325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27847,6 +27967,132 @@
         </is>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-35.1229513361716,173.97977150041459</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>-35.12292630615346,173.9807603824377</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>-35.12283229315633,173.9817256510997</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-35.122774726709686,173.98261704940606</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-35.12295301294302,173.9835120636887</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-35.12289919740235,173.9844101099937</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>-35.12295226160842,173.97977106626368</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>-35.12293749998647,173.9807557946044</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>-35.12282935530772,173.98172622465069</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-35.122767514982804,173.98261722033737</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-35.12294354579546,173.98351203166698</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>-35.12289000089946,173.9844100382931</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>-35.122965722507296,173.97976475134058</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>-35.12294288328016,173.98075358824136</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-35.122832204130624,173.98172566848004</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-35.12276778542256,173.98261721392745</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-35.122944717918486,173.98351203563158</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-35.12288747636926,173.9844100186106</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
